--- a/reports/二级子公司D_现金流量表_2026-11.xlsx
+++ b/reports/二级子公司D_现金流量表_2026-11.xlsx
@@ -1957,16 +1957,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
-      <c r="G3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
+      <c r="F3" s="28" t="n"/>
+      <c r="G3" s="28" t="n"/>
       <c r="I3" s="5" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1996,10 +1988,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>70136820</v>
+        <v>67855886</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>774975708</v>
+        <v>752006966</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2030,10 +2022,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>1395170</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>15982898</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2063,10 +2055,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>695638</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>7981472</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2096,10 +2088,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>347691</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>3996296</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2129,10 +2121,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>279126</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>3192596</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2162,10 +2154,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>208038</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>2397425</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2195,10 +2187,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>139856</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>1596740</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2228,10 +2220,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>103890</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>1198259</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2261,10 +2253,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>69944</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>798722</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2294,10 +2286,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>173289</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>1996189</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2327,10 +2319,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>87726</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>1003947</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2360,10 +2352,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>55236</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>634465</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2393,10 +2385,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>179838</v>
+        <v>174616</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>2063502</v>
+        <v>2004799</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2426,10 +2418,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>1198920</v>
+        <v>1165753</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>13756680</v>
+        <v>13346516</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2546,7 +2538,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>71515578</v>
+        <v>72751859</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2577,10 +2569,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>45958600</v>
+        <v>44411131</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>527339400</v>
+        <v>511920184</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2610,10 +2602,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>465846</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>5326378</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2643,10 +2635,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>347108</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>3991370</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2676,10 +2668,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>232297</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>2664025</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2709,10 +2701,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>174094</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>1995306</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2742,10 +2734,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>115780</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>1332077</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2775,10 +2767,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>87749</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>1002868</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2808,10 +2800,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>7193520</v>
+        <v>6953508</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>82540080</v>
+        <v>80173051</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2841,10 +2833,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>3796580</v>
+        <v>3704118</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>43562820</v>
+        <v>42282819</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2874,10 +2866,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>1498650</v>
+        <v>1447797</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>17195850</v>
+        <v>16695648</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2936,7 +2928,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>58447350</v>
+        <v>57939428</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2967,7 +2959,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>13068228</v>
+        <v>14812431</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -3093,10 +3085,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>82400</v>
+        <v>79701</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>906400</v>
+        <v>880521</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3159,10 +3151,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>721000</v>
+        <v>696511</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>7931000</v>
+        <v>7701583</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3192,10 +3184,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>432600</v>
+        <v>422036</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>4758600</v>
+        <v>4620148</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3225,7 +3217,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>803400</v>
+        <v>776212</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3256,10 +3248,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>8240000</v>
+        <v>8024982</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>90640000</v>
+        <v>88041561</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3289,10 +3281,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>1236000</v>
+        <v>1197944</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>13596000</v>
+        <v>13191695</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3322,10 +3314,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>5665000</v>
+        <v>5500687</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>62315000</v>
+        <v>60543577</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3454,10 +3446,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>185400</v>
+        <v>179139</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>2039400</v>
+        <v>1980701</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3487,7 +3479,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>8425400</v>
+        <v>8204121</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3518,7 +3510,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-7622000</v>
+        <v>-7427909</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3578,10 +3570,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>1545000</v>
+        <v>1495963</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>16995000</v>
+        <v>16491256</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3644,10 +3636,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>2575000</v>
+        <v>2501014</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>28325000</v>
+        <v>27479816</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3677,10 +3669,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>2575000</v>
+        <v>2495064</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>28325000</v>
+        <v>27519922</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3710,10 +3702,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>82400</v>
+        <v>80267</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>906400</v>
+        <v>879438</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3743,7 +3735,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>4202400</v>
+        <v>4077244</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3774,10 +3766,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>2060000</v>
+        <v>2009819</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>22660000</v>
+        <v>21993753</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3807,10 +3799,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>2060000</v>
+        <v>1990090</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>22660000</v>
+        <v>22001125</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3840,10 +3832,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>329600</v>
+        <v>321434</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>3625600</v>
+        <v>3520656</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3902,10 +3894,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>288400</v>
+        <v>280624</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>3172400</v>
+        <v>3081791</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3935,10 +3927,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>41200</v>
+        <v>39973</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>453200</v>
+        <v>439694</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3968,7 +3960,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>2430800</v>
+        <v>2371226</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3999,7 +3991,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>1771600</v>
+        <v>1706018</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -4059,7 +4051,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>7217828</v>
+        <v>9090540</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -4090,7 +4082,9 @@
         </is>
       </c>
       <c r="F69" s="23" t="n"/>
-      <c r="G69" s="20" t="n"/>
+      <c r="G69" s="20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
@@ -4119,7 +4113,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>7217828</v>
+        <v>9090540</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
